--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -647,12 +647,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Janice Lee</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -789,17 +789,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Winner of Match 3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Winner of Match 4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -838,17 +838,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -882,22 +882,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -936,17 +936,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Zain Merchant</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Zain Merchant</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Ryuto Leegomonchai</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 7</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra, Brandon Pham</t>
+          <t>Winner of Match 1, Winner of Match 2</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Midy Tao, Stephen Guan</t>
+          <t>Winner of Match 1, Winner of Match 2</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1267,57 +1267,53 @@
       <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Midy Tao / Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Midy Tao, Stephen Guan, Brandon Pham</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Rishi Jain</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1325,7 +1321,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1335,22 +1331,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Fanghong Huang</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1374,17 +1370,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Court 6</t>
+          <t>Court 5</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Winner of Match 3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Winner of Match 4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1423,7 +1419,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 6</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1443,7 +1439,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1468,36 +1464,36 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Shiyang Chang</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1531,22 +1527,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1570,32 +1566,32 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Zain Merchant</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1614,130 +1610,204 @@
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Meghan Wong / Makenna Wong</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Stephen Guan</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Ryuto Leegomonchai</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Fanghong Huang</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Court 7</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Winner of Match 1, Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1745,37 +1815,37 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Winner of Match 1, Winner of Match 2</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1798,17 +1868,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1818,12 +1888,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Vincent Onggoputra</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1847,17 +1917,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1867,12 +1937,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Winner of Match 3</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Winner of Match 4</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1891,151 +1961,34 @@
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Hanna Yun / Cynthia Liu</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee / Cindy Lim</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Fanghong Huang</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Shiyang Chang</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2043,7 +1996,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2053,7 +2006,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2063,12 +2016,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2092,32 +2045,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2141,32 +2094,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2190,32 +2143,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Court 6</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2239,32 +2192,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 5</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2283,57 +2236,53 @@
       <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Brandon Pham</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2341,32 +2290,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2390,17 +2339,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2410,12 +2359,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Shiyang Chang</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2434,204 +2383,44 @@
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" t="n">
         <v>7</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>7</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee / Cindy Lim</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Fanghong Huang</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2639,32 +2428,32 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2688,32 +2477,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2732,24 +2521,102 @@
       <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Brandon Pham / Irwin Sunarto</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Hancheng Li / Zhuoran Cheng</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang / Dominic Pang</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Yingchao Peng / Wenhao Zhang</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2757,7 +2624,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 5</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2634,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 6</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2644,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2792,17 +2659,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -2826,7 +2693,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2836,22 +2703,22 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -2870,200 +2737,44 @@
       <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" t="n">
         <v>9</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>9</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Midy Tao</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>9</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Shiyang Chang</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58"/>
     <row r="59">
@@ -3103,90 +2814,30 @@
       <c r="K60" s="5" t="inlineStr"/>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Winner of Match 1</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="F62" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Winner of Match 2</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Winner of Match #1</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Winner of Match #2</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Brandon Pham</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -647,12 +647,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -686,22 +686,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>Hancheng Li / Zhuoran Cheng</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>Edward Wang / Dominic Pang</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -779,12 +779,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 3</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 4</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -926,27 +926,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Winner of Match #3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Winner of Match #4</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>Haocheng Teng</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Winner of Match #1</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Winner of Match #2</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
+          <t>Winner of Match #1, Winner of Match #2</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Winner of Match #1</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Winner of Match #2</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
+          <t>Winner of Match #1, Winner of Match #2</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1326,27 +1326,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1390,12 +1390,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 3</t>
+          <t>Fanghong Huang</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 4</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1434,17 +1434,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Ryuto Leegomonchai</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1527,22 +1527,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Winner of Match #3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Winner of Match #4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1620,27 +1620,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Midy Tao</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -1659,110 +1659,75 @@
       <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Winner of Match #1</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Winner of Match #2</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Winner of Match #1, Winner of Match #2</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Fanghong Huang</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Court 7</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1772,7 +1737,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1782,17 +1747,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Winner of Match #1</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Winner of Match #2</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
+          <t>Winner of Match #1, Winner of Match #2</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1810,57 +1775,53 @@
       <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match 1, Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Yingchao Peng / Wenhao Zhang</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Brandon Pham / Irwin Sunarto</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1868,32 +1829,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1917,32 +1878,32 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 3</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 4</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1961,34 +1922,151 @@
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Stephen Guan</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Onggoputra</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Hanna Yun / Cynthia Liu</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1996,7 +2074,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2006,7 +2084,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2016,12 +2094,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2045,32 +2123,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2094,17 +2172,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2114,12 +2192,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Shiyang Chang</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Janice Lee</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2143,17 +2221,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 5</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2163,12 +2241,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Winner of Match #3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Winner of Match #4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2187,61 +2265,22 @@
       <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Court 6</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2261,12 +2300,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Winner of Match #1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Winner of Match #2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2290,17 +2329,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2310,12 +2349,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2339,32 +2378,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Shiyang Chang</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2383,24 +2422,102 @@
       <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>BYE</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2408,215 +2525,98 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Yingchao Peng / Wenhao Zhang</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang / Dominic Pang</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>8</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Court 5</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>7</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung / Jason Liu</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang / Dominic Pang</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2624,19 +2624,58 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 6</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>8</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Match #1</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Match #2</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2644,7 +2683,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2654,22 +2693,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match 2</t>
+          <t>BYE</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -2688,53 +2727,14 @@
       <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>9</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 4</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 5</t>
         </is>
       </c>
     </row>
@@ -2762,80 +2762,70 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>9</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
           <t>Court 6</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr"/>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+    </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr"/>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="4" t="inlineStr"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Total Affected Players</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Total Affected Players</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="n">
-        <v>2</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Winner of Match #1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="F61" t="inlineStr">
         <is>
-          <t>Winner of Match 1</t>
+          <t>Winner of Match #2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
         <is>
           <t>Consecutive 4 times</t>
         </is>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,13 +453,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #2</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -583,27 +583,27 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -632,27 +632,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -789,17 +789,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Yijun Liu</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -877,27 +877,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -916,208 +916,224 @@
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Ryuto Leegomonchai</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Charles Yang / Haipeng Huang</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Midy Tao / Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Vincent Onggoputra</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Haocheng Teng</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Martin Lee</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Court 7</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1127,27 +1143,27 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #2</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #1, Winner of Match #2</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1170,7 +1186,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1190,17 +1206,17 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Zain Merchant</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #2</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #1, Winner of Match #2</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1223,17 +1239,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1243,12 +1259,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1272,17 +1288,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1292,12 +1308,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1321,7 +1337,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 5</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1331,22 +1347,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1365,298 +1381,322 @@
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar, Heng Wu, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Haonan Wang, Avi Aswal, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Jason Liu, Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Elisa Liu, Reyna Wan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Yuhung Kung, Jason Liu, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Fanghong Huang</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Ryuto Leegomonchai</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee / Cindy Lim</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Hanna Yun / Cynthia Liu</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Meghan Wong / Makenna Wong</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #3</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #4</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Midy Tao</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1664,37 +1704,37 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 6</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #2</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Winner of Match #1, Winner of Match #2</t>
+          <t>Aryan Khandekar, Heng Wu, Jason Liu, Yuhung Kung</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1712,67 +1752,106 @@
       <c r="M25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng, Aryan Khandekar, Heng Wu, Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Winner of Match #1, Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1780,7 +1859,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1800,12 +1879,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1829,32 +1908,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1878,17 +1957,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 5</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1898,12 +1977,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1927,7 +2006,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 6</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1942,17 +2021,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>BYE</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -1972,11 +2051,11 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Court 6</t>
+          <t>Court 1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1996,12 +2075,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -2025,7 +2104,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2035,7 +2114,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2045,12 +2124,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2074,32 +2153,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2123,32 +2202,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Court 3</t>
+          <t>Court 4</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2172,7 +2251,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Court 4</t>
+          <t>Court 5</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2182,7 +2261,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2192,12 +2271,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Shiyang Chang</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2221,7 +2300,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Court 5</t>
+          <t>Court 6</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2231,22 +2310,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #3</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #4</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2265,14 +2344,53 @@
       <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2280,17 +2398,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Court 1</t>
+          <t>Court 2</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2300,12 +2418,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Winner of Match #2</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2329,17 +2447,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Court 2</t>
+          <t>Court 3</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2349,12 +2467,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2373,461 +2491,241 @@
       <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>7</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>7</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yuhung Kung / Jason Liu</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>7</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>7</v>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang / Dominic Pang</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>8</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Total Affected Players</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>8</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Court 3</t>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>8</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Court 4</t>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>8</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Court 5</t>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>8</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Court 6</t>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #1</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>BYE</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>9</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Court 3</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>9</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Court 4</t>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>9</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Court 5</t>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>9</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Elisa Liu</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr"/>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Reyna Wan</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Total Affected Players</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="n">
-        <v>2</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="F60" t="inlineStr">
         <is>
-          <t>Winner of Match #1</t>
+          <t>Juncheng Tang</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Winner of Match #2</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
+          <t>Consecutive 1 times</t>
         </is>
       </c>
     </row>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -637,22 +637,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -686,22 +686,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Avi Aswal, Haonan Wang</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Midy Tao</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Vincent Onggoputra</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Aryan Khandekar, Heng Wu, Manmeeth Nagesh</t>
+          <t>Juncheng Tang, Yifei Zheng, Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Elisa Liu, Reyna Wan</t>
+          <t>Reyna Wan, Elisa Liu</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Avi Aswal, Haonan Wang</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Aryan Khandekar, Heng Wu, Jason Liu, Yuhung Kung</t>
+          <t>Jason Liu, Juncheng Tang, Yifei Zheng, Yuhung Kung</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Aryan Khandekar, Heng Wu, Juncheng Tang</t>
+          <t>Juncheng Tang, Aryan Khandekar, Heng Wu, Yifei Zheng</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
     <row r="47">
       <c r="F47" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -2576,7 +2576,7 @@
     <row r="48">
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -2600,7 +2600,7 @@
     <row r="50">
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aryan Khandekar</t>
+          <t>Juncheng Tang</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="51">
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heng Wu</t>
+          <t>Yifei Zheng</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2660,7 +2660,7 @@
     <row r="55">
       <c r="F55" t="inlineStr">
         <is>
-          <t>Midy Tao</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="57">
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elisa Liu</t>
+          <t>Reyna Wan</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="58">
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reyna Wan</t>
+          <t>Elisa Liu</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="59">
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yifei Zheng</t>
+          <t>Aryan Khandekar</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -2720,7 +2720,7 @@
     <row r="60">
       <c r="F60" t="inlineStr">
         <is>
-          <t>Juncheng Tang</t>
+          <t>Heng Wu</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +603,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang / Dominic Pang</t>
+          <t>Midy Tao / Stephen Guan</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -833,22 +833,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Yijun Liu</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Ines Bocanegra</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -887,17 +887,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Edward Wang</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -916,110 +916,102 @@
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lee</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal, Haonan Wang</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Haocheng Teng</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Ryuto Leegomonchai</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1032,32 +1024,32 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1095,22 +1087,22 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Zain Merchant</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1128,159 +1120,155 @@
       <c r="M13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Stephen Guan</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Onggoputra</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Yijun Liu</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Avi Aswal</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Haocheng Teng</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Zain Merchant</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Haonan Wang</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Midy Tao</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Vincent Onggoputra</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang, Avi Aswal</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1308,12 +1296,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1411,12 +1399,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Yifei Zheng, Manmeeth Nagesh</t>
+          <t>Manmeeth Nagesh, Aryan Khandekar, Heng Wu</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1469,7 +1457,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Haonan Wang, Avi Aswal, Manmeeth Nagesh</t>
+          <t>Haonan Wang, Manmeeth Nagesh, Prathamesh Koranne, Avi Aswal</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1517,7 +1505,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1575,7 +1563,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan, Elisa Liu</t>
+          <t>Elisa Liu, Reyna Wan</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1628,7 +1616,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Yuhung Kung, Jason Liu, Manmeeth Nagesh</t>
+          <t>Yuhung Kung, Manmeeth Nagesh, Prathamesh Koranne, Jason Liu</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1676,12 +1664,12 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal, Haonan Wang</t>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1729,12 +1717,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Jason Liu, Juncheng Tang, Yifei Zheng, Yuhung Kung</t>
+          <t>Jason Liu, Yuhung Kung, Aryan Khandekar, Heng Wu</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1787,7 +1775,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Aryan Khandekar, Heng Wu, Yifei Zheng</t>
+          <t>Yifei Zheng, Juncheng Tang, Heng Wu, Aryan Khandekar</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1820,12 +1808,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1913,12 +1901,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2021,7 +2009,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2119,7 +2107,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2212,7 +2200,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2256,17 +2244,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2305,17 +2293,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2364,7 +2352,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2403,12 +2391,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2558,13 +2546,13 @@
       <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="F47" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -2576,7 +2564,7 @@
     <row r="48">
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -2600,7 +2588,7 @@
     <row r="50">
       <c r="F50" t="inlineStr">
         <is>
-          <t>Juncheng Tang</t>
+          <t>Aryan Khandekar</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -2612,7 +2600,7 @@
     <row r="51">
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yifei Zheng</t>
+          <t>Heng Wu</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2660,7 +2648,7 @@
     <row r="55">
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Elisa Liu</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -2672,7 +2660,7 @@
     <row r="56">
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Reyna Wan</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -2684,7 +2672,7 @@
     <row r="57">
       <c r="F57" t="inlineStr">
         <is>
-          <t>Reyna Wan</t>
+          <t>Yifei Zheng</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -2696,34 +2684,10 @@
     <row r="58">
       <c r="F58" t="inlineStr">
         <is>
-          <t>Elisa Liu</t>
+          <t>Juncheng Tang</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Heng Wu</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +603,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Midy Tao / Stephen Guan</t>
+          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Brandon Pham / Irwin Sunarto</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -838,17 +838,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Vincent Onggoputra</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -887,17 +887,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Zain Merchant</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Rishi Jain</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -980,22 +980,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Fanghong Huang</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Shiyang Chang</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Zain Merchant</t>
+          <t>Ryuto Leegomonchai</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1140,17 +1140,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Dominic Pang</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1169,53 +1169,57 @@
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Yijun Liu</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1243,17 +1247,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
           <t>Avi Aswal</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1281,12 +1285,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1296,12 +1300,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1330,27 +1334,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Brandon Pham</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Edward Wang</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1394,7 +1398,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1404,7 +1408,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh, Aryan Khandekar, Heng Wu</t>
+          <t>Yifei Zheng, Juncheng Tang</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1452,12 +1456,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Manmeeth Nagesh, Prathamesh Koranne, Avi Aswal</t>
+          <t>Manmeeth Nagesh, Jason Liu</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1500,17 +1504,17 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Jason Liu, Yuhung Kung</t>
+          <t>Heng Wu, Haonan Wang, Avi Aswal, Aryan Khandekar</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1563,7 +1567,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Elisa Liu, Reyna Wan</t>
+          <t>Reyna Wan, Elisa Liu</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1611,12 +1615,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Manmeeth Nagesh, Prathamesh Koranne, Jason Liu</t>
+          <t>Manmeeth Nagesh, Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1669,7 +1673,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Juncheng Tang, Yifei Zheng, Jason Liu</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1722,7 +1726,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Jason Liu, Yuhung Kung, Aryan Khandekar, Heng Wu</t>
+          <t>Heng Wu, Jason Liu, Aryan Khandekar</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1765,17 +1769,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
           <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Juncheng Tang, Heng Wu, Aryan Khandekar</t>
+          <t>Prathamesh Koranne, Yifei Zheng, Manmeeth Nagesh, Juncheng Tang</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1852,17 +1856,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1906,12 +1910,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1960,17 +1964,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 3</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 4</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -1989,705 +1993,195 @@
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 3</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 4</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 3</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 4</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total Affected Players</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Consecutive 4 times</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Court 4</t>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Court 5</t>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Reyna Wan</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
-      <c r="M45" s="4" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Elisa Liu</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Total Affected Players</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr"/>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Heng Wu</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="F54" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Elisa Liu</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Reyna Wan</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,7 +603,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Midy Tao / Stephen Guan</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Edward Wang / Dominic Pang</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham / Irwin Sunarto</t>
+          <t>Hanna Yun / Cynthia Liu</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Charles Yang / Haipeng Huang</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Hancheng Li / Zhuoran Cheng</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -843,12 +843,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Stephen Guan</t>
+          <t>Brandon Pham</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Ryuto Leegomonchai</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -931,22 +931,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Ines Bocanegra</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Shiyang Chang</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -980,22 +980,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>WS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Fanghong Huang</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Shiyang Chang</t>
+          <t>Shan Zhong</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1039,17 +1039,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Yuhung Kung, Jason Liu</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1169,57 +1169,53 @@
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Vincent Onggoputra</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1247,17 +1243,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1275,53 +1271,57 @@
       <c r="M16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Court 4</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Meghan Wong / Makenna Wong</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1334,27 +1334,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Brandon Pham</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1373,57 +1373,53 @@
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Heng Wu / Aryan Khandekar</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng, Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Midy Tao</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Stephen Guan</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1461,7 +1457,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh, Jason Liu</t>
+          <t>Jason Liu, Yuhung Kung</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1509,12 +1505,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Haonan Wang, Avi Aswal, Aryan Khandekar</t>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1557,17 +1553,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
+          <t>Meghan Wong / Makenna Wong</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
           <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Reyna Wan / Elisa Liu</t>
-        </is>
-      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan, Elisa Liu</t>
+          <t>Bernice Tse Ling Tung, Tsz Ching Chen</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1620,7 +1616,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh, Haonan Wang, Avi Aswal</t>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1673,7 +1669,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Juncheng Tang, Yifei Zheng, Jason Liu</t>
+          <t>Yuhung Kung, Jason Liu</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1716,7 +1712,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1726,7 +1722,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Jason Liu, Aryan Khandekar</t>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1774,12 +1770,12 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Yifei Zheng, Manmeeth Nagesh, Juncheng Tang</t>
+          <t>Heng Wu, Manmeeth Nagesh, Aryan Khandekar, Prathamesh Koranne</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1797,53 +1793,57 @@
       <c r="M26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu, Aryan Khandekar, Juncheng Tang, Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 3</t>
+          <t>Winner of Winner of Match 1</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 4</t>
+          <t>Winner of Winner of Match 2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 1</t>
+          <t>Winner of Winner of Match 3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 2</t>
+          <t>Winner of Winner of Match 4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1993,195 +1993,372 @@
       <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-    </row>
-    <row r="32"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Total Affected Players</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="n">
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Yifei Zheng</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
       </c>
     </row>
     <row r="41">
       <c r="F41" t="inlineStr">
         <is>
-          <t>Heng Wu</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aryan Khandekar</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="F44" t="inlineStr">
         <is>
-          <t>Reyna Wan</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elisa Liu</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 2 times</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="F46" t="inlineStr">
         <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Prathamesh Koranne</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -598,12 +598,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -696,12 +696,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Edward Wang / Dominic Pang</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Midy Tao / Stephen Guan</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang / Dominic Pang</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,22 +735,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Hanna Yun / Cynthia Liu</t>
+          <t>Shan Zhong / Fanghong Huang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Martin Lee / Anais Molinaro</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Yingchao Peng / Wenhao Zhang</t>
+          <t>Zhuoran Cheng / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hancheng Li / Zhuoran Cheng</t>
+          <t>Yantao Fang / Shiyang Chang</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -818,53 +818,57 @@
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Brandon Pham</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -877,27 +881,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Zain Merchant</t>
+          <t>Yingchao Peng / Wenhao Zhang</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Ryuto Leegomonchai</t>
+          <t>Charles Yang / Haipeng Huang</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -916,102 +920,110 @@
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Janice Lee / Cindy Lim</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Yen Zhen Tan</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Ines Bocanegra</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Shiyang Chang</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Martin Lee</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Shan Zhong</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Zain Merchant</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Haonan Wang</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1024,12 +1036,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1039,17 +1051,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Haocheng Teng</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Jason Liu</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1092,17 +1104,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Ryuto Leegomonchai</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Haocheng Teng</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1130,27 +1142,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1189,17 +1201,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Edward Wang</t>
+          <t>Martin Lee</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Vincent Onggoputra</t>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -1218,57 +1230,53 @@
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Edward Wang</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Rishi Jain</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1281,12 +1289,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Double</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1296,17 +1304,17 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Prathamesh Koranne, Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1334,27 +1342,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Stephen Guan</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Vincent Onggoputra</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1373,53 +1381,57 @@
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>WS</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Midy Tao</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Stephen Guan</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Shiyang Chang</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1432,12 +1444,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1447,17 +1459,17 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Avi Aswal</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Jason Liu, Yuhung Kung</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1475,57 +1487,53 @@
       <c r="M20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Court 2</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Avi Aswal / Haonan Wang</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Haonan Wang, Avi Aswal</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1543,7 +1551,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1553,17 +1561,17 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung, Tsz Ching Chen</t>
+          <t>Yifei Zheng, Juncheng Tang</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1596,7 +1604,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1606,17 +1614,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Meghan Wong, Prathamesh Koranne</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1659,17 +1667,17 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
           <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Jason Liu</t>
+          <t>Prathamesh Koranne, Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1717,12 +1725,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Haonan Wang, Avi Aswal</t>
+          <t>Yifei Zheng, Juncheng Tang</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1755,7 +1763,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1765,17 +1773,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Manmeeth Nagesh, Aryan Khandekar, Prathamesh Koranne</t>
+          <t>Meghan Wong, Elisa Liu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1818,17 +1826,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Aryan Khandekar, Juncheng Tang, Yifei Zheng</t>
+          <t>Prathamesh Koranne, Avi Aswal, Haonan Wang, Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1846,519 +1854,862 @@
       <c r="M27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung / Jason Liu</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Yuhung Kung, Jason Liu</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne / Meghan Wong</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Meghan Wong, Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>XD</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Junjie Zhou / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Yifei Zheng</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng, Elisa Liu, Junjie Zhou</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Avi Aswal / Haonan Wang</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu, Avi Aswal, Haonan Wang, Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Heng Wu / Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng, Heng Wu, Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan / Elisa Liu</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Reyna Wan, Elisa Liu, Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 1</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Winner of Winner of Match 2</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Court 5</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 3</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 4</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Court 6</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Winner of Winner of Match 2</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Court 4</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 3</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 4</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Court 5</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Court 2</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 1</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Winner of Winner of Match 2</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Court 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Court 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Court 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Stats</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr"/>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Total Affected Players</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr"/>
-      <c r="C40" s="5" t="inlineStr"/>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Yuhung Kung</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Jason Liu</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Consecutive 4 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Haonan Wang</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Avi Aswal</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Consecutive 3 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Heng Wu</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Consecutive 2 times</t>
-        </is>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aryan Khandekar</t>
+          <t>Prathamesh Koranne</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 6 times</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung</t>
+          <t>Yifei Zheng</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 5 times</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tsz Ching Chen</t>
+          <t>Manmeeth Nagesh</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 4 times</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne</t>
+          <t>Haonan Wang</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="F51" t="inlineStr">
         <is>
-          <t>Juncheng Tang</t>
+          <t>Meghan Wong</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Consecutive 1 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yifei Zheng</t>
+          <t>Elisa Liu</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
+        <is>
+          <t>Consecutive 3 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yuhung Kung</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jason Liu</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Avi Aswal</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Heng Wu</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Aryan Khandekar</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Consecutive 2 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yen Zhen Tan</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Janice Lee</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Junjie Zhou</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Reyna Wan</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Consecutive 1 times</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bernice Tse Ling Tung</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>

--- a/instance/tournament_1_schedule.xlsx
+++ b/instance/tournament_1_schedule.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,7 +707,7 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Zhuoran Cheng / Yen Zhen Tan</t>
+          <t>Sirui Jiang / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Yantao Fang / Shiyang Chang</t>
+          <t>Janice Lee / Cindy Lim</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Sirui Jiang / Yen Zhen Tan</t>
+          <t>Zhuoran Cheng / Yen Zhen Tan</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Janice Lee / Cindy Lim</t>
+          <t>Yantao Fang / Shiyang Chang</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Martin Lee</t>
+          <t>Edward Wang</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Gustavo Adolpho Lucas de Carvalho</t>
+          <t>Rishi Jain</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -1230,106 +1230,106 @@
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Court 3</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Yifei Zheng / Juncheng Tang</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Prathamesh Koranne, Manmeeth Nagesh</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Edward Wang</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Rishi Jain</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Court 4</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Manmeeth Nagesh / Prathamesh Koranne</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Prathamesh Koranne, Manmeeth Nagesh</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Martin Lee</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Gustavo Adolpho Lucas de Carvalho</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1381,57 +1381,53 @@
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Court 6</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>WS</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Shiyang Chang</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Janice Lee</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Shan Zhong</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Pang</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1502,22 +1498,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>WS</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Shan Zhong</t>
+          <t>Shiyang Chang</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Dominic Pang</t>
+          <t>Janice Lee</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1571,7 +1567,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Juncheng Tang</t>
+          <t>Juncheng Tang, Yifei Zheng</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1619,12 +1615,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Junjie Zhou / Elisa Liu</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong, Prathamesh Koranne</t>
+          <t>Meghan Wong, Bernice Tse Ling Tung, Prathamesh Koranne</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1672,7 +1668,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1682,14 +1678,14 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
@@ -1710,7 +1706,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1720,17 +1716,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Bernice Tse Ling Tung / Yang Jiao</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng / Juncheng Tang</t>
+          <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Juncheng Tang</t>
+          <t>Bernice Tse Ling Tung, Yifei Zheng</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1763,7 +1759,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1773,17 +1769,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong / Makenna Wong</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan / Elisa Liu</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong, Elisa Liu</t>
+          <t>Yuhung Kung, Jason Liu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1831,24 +1827,24 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Yuhung Kung / Jason Liu</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne, Avi Aswal, Haonan Wang, Manmeeth Nagesh</t>
+          <t>Yuhung Kung, Prathamesh Koranne, Manmeeth Nagesh, Jason Liu</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Finished</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr"/>
@@ -1869,7 +1865,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1879,17 +1875,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan / Yifei Zheng</t>
+          <t>Yifei Zheng / Juncheng Tang</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng</t>
+          <t>Haonan Wang, Juncheng Tang, Avi Aswal, Yifei Zheng</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1922,7 +1918,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>WD</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1932,17 +1928,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung / Jason Liu</t>
+          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Reyna Wan / Elisa Liu</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Yuhung Kung, Jason Liu</t>
+          <t>Reyna Wan, Bernice Tse Ling Tung</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1985,17 +1981,17 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Prathamesh Koranne / Meghan Wong</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Yang Jiao</t>
+          <t>Reyna Wan / Yifei Zheng</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Meghan Wong, Prathamesh Koranne</t>
+          <t>Reyna Wan, Yifei Zheng</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -2028,7 +2024,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>XD</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2038,17 +2034,17 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Junjie Zhou / Elisa Liu</t>
+          <t>Avi Aswal / Haonan Wang</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan / Yifei Zheng</t>
+          <t>Heng Wu / Aryan Khandekar</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Elisa Liu, Junjie Zhou</t>
+          <t>Haonan Wang, Avi Aswal</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2081,7 +2077,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>XD</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2091,17 +2087,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Avi Aswal / Haonan Wang</t>
+          <t>Prathamesh Koranne / Meghan Wong</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu / Aryan Khandekar</t>
+          <t>Junjie Zhou / Elisa Liu</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Heng Wu, Avi Aswal, Haonan Wang, Aryan Khandekar</t>
+          <t>Junjie Zhou, Elisa Liu, Prathamesh Koranne</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -2154,7 +2150,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Yifei Zheng, Heng Wu, Aryan Khandekar</t>
+          <t>Heng Wu, Juncheng Tang, Aryan Khandekar, Yifei Zheng</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2197,7 +2193,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bernice Tse Ling Tung / Tsz Ching Chen</t>
+          <t>Meghan Wong / Makenna Wong</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2207,7 +2203,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Reyna Wan, Elisa Liu, Bernice Tse Ling Tung</t>
+          <t>Elisa Liu, Reyna Wan</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2245,7 +2241,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2343,12 +2339,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Winner of Winner of Match 1</t>
+          <t>Winner of Winner of Match #1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2508,7 +2504,7 @@
       <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -2562,7 +2558,7 @@
     <row r="51">
       <c r="F51" t="inlineStr">
         <is>
-          <t>Meghan Wong</t>
+          <t>Yuhung Kung</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -2574,7 +2570,7 @@
     <row r="52">
       <c r="F52" t="inlineStr">
         <is>
-          <t>Elisa Liu</t>
+          <t>Jason Liu</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -2586,36 +2582,36 @@
     <row r="53">
       <c r="F53" t="inlineStr">
         <is>
-          <t>Yuhung Kung</t>
+          <t>Juncheng Tang</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jason Liu</t>
+          <t>Bernice Tse Ling Tung</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="F55" t="inlineStr">
         <is>
-          <t>Juncheng Tang</t>
+          <t>Reyna Wan</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 3 times</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2630,7 @@
     <row r="57">
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heng Wu</t>
+          <t>Elisa Liu</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -2646,19 +2642,19 @@
     <row r="58">
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aryan Khandekar</t>
+          <t>Yen Zhen Tan</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Consecutive 2 times</t>
+          <t>Consecutive 1 times</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yen Zhen Tan</t>
+          <t>Meghan Wong</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -2670,7 +2666,7 @@
     <row r="60">
       <c r="F60" t="inlineStr">
         <is>
-          <t>Janice Lee</t>
+          <t>Junjie Zhou</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -2682,7 +2678,7 @@
     <row r="61">
       <c r="F61" t="inlineStr">
         <is>
-          <t>Junjie Zhou</t>
+          <t>Heng Wu</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -2694,22 +2690,10 @@
     <row r="62">
       <c r="F62" t="inlineStr">
         <is>
-          <t>Reyna Wan</t>
+          <t>Aryan Khandekar</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
-        <is>
-          <t>Consecutive 1 times</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Bernice Tse Ling Tung</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
         <is>
           <t>Consecutive 1 times</t>
         </is>
